--- a/events/Szeged_2020_WC/Szeged_2020_WC_Results.xlsx
+++ b/events/Szeged_2020_WC/Szeged_2020_WC_Results.xlsx
@@ -604,6 +604,11 @@
           <t>1:06.16</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -810,6 +815,11 @@
           <t>1:06.69</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>80554</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -872,6 +882,11 @@
           <t>59.56</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2405,6 +2420,11 @@
           <t>+12.35</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3785,6 +3805,11 @@
           <t>+6.30</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6395,6 +6420,11 @@
           <t>44.55</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7304,6 +7334,11 @@
           <t>+4.46</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>100250</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7924,6 +7959,11 @@
           <t>+54.32</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9444,6 +9484,11 @@
           <t>+7.98</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10964,6 +11009,11 @@
           <t>+1.22</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11444,6 +11494,11 @@
           <t>+16.46</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11509,6 +11564,11 @@
           <t>+21.49</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13179,6 +13239,11 @@
           <t>+24.83</t>
         </is>
       </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13864,6 +13929,11 @@
           <t>+16.65</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14069,6 +14139,11 @@
           <t>36175</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14734,6 +14809,11 @@
           <t>58046</t>
         </is>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14949,6 +15029,11 @@
           <t>+6.46</t>
         </is>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>46375</t>
@@ -15244,6 +15329,11 @@
           <t>53480</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16979,6 +17069,11 @@
           <t>+22.40</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -18774,6 +18869,11 @@
           <t>+12.74</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18839,6 +18939,11 @@
           <t>+13.90</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -20259,6 +20364,11 @@
           <t>53480</t>
         </is>
       </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -22019,6 +22129,11 @@
           <t>4:29.07</t>
         </is>
       </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -23482,6 +23597,11 @@
           <t>+17.51</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>80554</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -24110,6 +24230,11 @@
           <t>+7.78</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -24250,6 +24375,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>64463</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -26290,6 +26420,11 @@
           <t>+0.24</t>
         </is>
       </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -27185,6 +27320,11 @@
           <t>+7.89</t>
         </is>
       </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -29055,6 +29195,11 @@
           <t>+21.62</t>
         </is>
       </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -29195,6 +29340,11 @@
           <t>36180</t>
         </is>
       </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -29340,6 +29490,11 @@
           <t>58046</t>
         </is>
       </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -29405,6 +29560,11 @@
           <t>+13.56</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
           <t>46375</t>
@@ -30150,6 +30310,11 @@
           <t>36175</t>
         </is>
       </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -31325,6 +31490,11 @@
           <t>4:34.85</t>
         </is>
       </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -31390,6 +31560,11 @@
           <t>+3.78</t>
         </is>
       </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -31660,6 +31835,11 @@
           <t>43.08</t>
         </is>
       </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -32025,6 +32205,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -34065,6 +34250,11 @@
           <t>+0.28</t>
         </is>
       </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
       <c r="S478" t="inlineStr">
         <is>
           <t>36143</t>
@@ -35755,6 +35945,11 @@
           <t>43.19</t>
         </is>
       </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -38245,6 +38440,11 @@
           <t>50.52</t>
         </is>
       </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -39482,6 +39682,11 @@
           <t>2:43.76</t>
         </is>
       </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -39688,6 +39893,11 @@
           <t>2:51.59</t>
         </is>
       </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>80554</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -39750,6 +39960,11 @@
           <t>2:34.83</t>
         </is>
       </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -40918,6 +41133,11 @@
           <t>+2.36</t>
         </is>
       </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S576" t="inlineStr">
         <is>
           <t>46375</t>
@@ -42833,6 +43053,11 @@
           <t>+1.71</t>
         </is>
       </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -43332,6 +43557,11 @@
           <t>+29.42</t>
         </is>
       </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -44963,6 +45193,11 @@
           <t>+3.30</t>
         </is>
       </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>100250</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -47448,6 +47683,11 @@
           <t>+0.61</t>
         </is>
       </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -48585,6 +48825,11 @@
           <t>+1.62</t>
         </is>
       </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -50010,6 +50255,11 @@
           <t>+3.91</t>
         </is>
       </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -50504,6 +50754,11 @@
           <t>+4.63</t>
         </is>
       </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -50715,6 +50970,11 @@
           <t>+11.45</t>
         </is>
       </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -50854,6 +51114,11 @@
           <t>+15.28</t>
         </is>
       </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -52483,6 +52748,11 @@
           <t>36175</t>
         </is>
       </c>
+      <c r="S737" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -52709,6 +52979,11 @@
           <t>58046</t>
         </is>
       </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -52776,6 +53051,11 @@
           <t>+4.65</t>
         </is>
       </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S741" t="inlineStr">
         <is>
           <t>46375</t>
@@ -53068,6 +53348,11 @@
           <t>53480</t>
         </is>
       </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -55223,6 +55508,11 @@
           <t>+8.95</t>
         </is>
       </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -56048,6 +56338,11 @@
           <t>+1.08</t>
         </is>
       </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -57203,6 +57498,11 @@
           <t>58046</t>
         </is>
       </c>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -57273,6 +57573,11 @@
           <t>36175</t>
         </is>
       </c>
+      <c r="S804" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -57713,6 +58018,11 @@
           <t>+41.98</t>
         </is>
       </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S810" t="inlineStr">
         <is>
           <t>46375</t>
@@ -58333,6 +58643,11 @@
           <t>39.57</t>
         </is>
       </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -59101,6 +59416,11 @@
           <t>+18.32</t>
         </is>
       </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>80554</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -59657,6 +59977,11 @@
           <t>+10.79</t>
         </is>
       </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -59929,6 +60254,11 @@
           <t>+1.98</t>
         </is>
       </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -63214,9 +63544,24 @@
           <t>1:36.00</t>
         </is>
       </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
       <c r="S885" t="inlineStr">
         <is>
           <t>36171</t>
+        </is>
+      </c>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -64924,6 +65269,11 @@
           <t>+0.24</t>
         </is>
       </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
       <c r="S908" t="inlineStr">
         <is>
           <t>36143</t>
@@ -67919,6 +68269,11 @@
           <t>+1.24</t>
         </is>
       </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -69513,6 +69868,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S970" t="inlineStr">
+        <is>
+          <t>64463</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -70156,6 +70516,11 @@
           <t>+2.70</t>
         </is>
       </c>
+      <c r="R979" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -70978,6 +71343,11 @@
           <t>36180</t>
         </is>
       </c>
+      <c r="S990" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -71435,6 +71805,11 @@
           <t>36175</t>
         </is>
       </c>
+      <c r="S996" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -71507,6 +71882,11 @@
           <t>58046</t>
         </is>
       </c>
+      <c r="S997" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -71646,6 +72026,11 @@
           <t>40.09</t>
         </is>
       </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -72289,6 +72674,11 @@
           <t>53480</t>
         </is>
       </c>
+      <c r="S1008" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
@@ -73126,6 +73516,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S1019" t="inlineStr">
+        <is>
+          <t>64463</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -74457,9 +74852,24 @@
           <t>+2.59</t>
         </is>
       </c>
+      <c r="R1037" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
       <c r="S1037" t="inlineStr">
         <is>
           <t>36171</t>
+        </is>
+      </c>
+      <c r="T1037" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
+      <c r="U1037" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -76379,6 +76789,11 @@
       <c r="L1061" t="n">
         <v>4</v>
       </c>
+      <c r="R1061" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
       <c r="X1061" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -76451,6 +76866,11 @@
           <t>42117</t>
         </is>
       </c>
+      <c r="S1062" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -76595,6 +77015,11 @@
           <t>+0.99</t>
         </is>
       </c>
+      <c r="R1064" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -78372,6 +78797,11 @@
           <t>+3:02.85</t>
         </is>
       </c>
+      <c r="R1088" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -78866,6 +79296,11 @@
           <t>+1:13.29</t>
         </is>
       </c>
+      <c r="R1095" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -80325,6 +80760,11 @@
           <t>+38.43</t>
         </is>
       </c>
+      <c r="R1116" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
@@ -82231,6 +82671,11 @@
       </c>
       <c r="L1143" t="n">
         <v>16</v>
+      </c>
+      <c r="R1143" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
       </c>
       <c r="X1143" t="inlineStr">
         <is>
@@ -82249,7 +82694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89754,6 +90199,424 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Mikhail</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>PAVLOV</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Vitaliy</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>VERHELES</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>KOROBEYNIKOV</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>MIRONCHENKO</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>52656</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Olesia</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ROMASENKO</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Raquel</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>DA COSTA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Larisa</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>VOLIK</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Sumit</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SHOKEEN</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>64463</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Daria</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>KHARCHENKO</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>72136</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>PLESCA</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>79481</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>DOLGOVA</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>80554</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>CHUPROV</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>100250</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Maksim</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>POPOV</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2020_WC/Szeged_2020_WC_Results.xlsx
+++ b/events/Szeged_2020_WC/Szeged_2020_WC_Results.xlsx
@@ -16439,6 +16439,11 @@
           <t>79148</t>
         </is>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20074,6 +20079,11 @@
           <t>79148</t>
         </is>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -42611,6 +42621,11 @@
           <t>79148</t>
         </is>
       </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -80403,6 +80418,11 @@
       <c r="Q1111" t="inlineStr">
         <is>
           <t>+0.81</t>
+        </is>
+      </c>
+      <c r="R1111" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -82694,7 +82714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D360"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90617,6 +90637,28 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
